--- a/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>A施力給B,B同時施給A的力是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>向前推人</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>反作用力</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>作用力與反作用力大小？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>反作用力</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>作用力與反作用力方向？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>相反</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>反向</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>作用反作用力作用在？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>不同物體</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>第三</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>兩物</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>作用反作用力會抵消嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不會</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>不同物體</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>走路時腳推地,地會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>推人前進</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>反作用力</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>火箭噴氣向下,火箭？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>向前推人</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>向上</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>牛頓第幾定律講作用反作用？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>第三</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>向前推船</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>牛頓第三定律說作用與反作用力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>大小相等方向相反</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>地球(人吸引地球)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>受力相等,小車加速度較大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>槍發射子彈槍後座是因為？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>反作用力</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反作用</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>划船槳向後推水,水？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>向前推船</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相等</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>第三</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>作用反作用力同時發生嗎？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>向前推人</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>同時</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>人推牆10N,牆推人？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>作用在不同物體上</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>10N</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>作用反作用與平衡力差在？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>受力物不同</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>關鍵</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>氣球放氣飛走靠？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>向前推人</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>反作用力</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>噴氣</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>大卡車撞小車彼此受力大小？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>反作用力</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>第三定律</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>游泳手向後划,水？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>反作用力</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>受力物不同</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>向前推人</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>為何作用反作用不抵消？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相同,皆反作用力推進</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>作用在不同物體</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>拍手時左右手受力大小？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>相等</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>走路時使人前進的是地面的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>反作用力</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>向前推船</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>不會</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>相反</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反作用</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上2-3 牛頓第三運動定律　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>火箭在太空無空氣為何仍能前進？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>噴氣的反作用力推火箭</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>平衡力同一物體、作用反作用不同物體</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>受力相等,小車加速度較大</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>相同,皆反作用力推進</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>大車與小車相撞誰受力大?加速度呢？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>受力相等,小車加速度較大</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>地面對腳的反作用力</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>平衡力同一物體、作用反作用不同物體</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>槳推水與水推槳</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>第二三定律</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>如何區分平衡力與作用反作用力？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>平衡力同一物體、作用反作用不同物體</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>地球(人吸引地球)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>槳推水與水推槳</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>區別</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>走路時真正使人前進的力來自？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>地面對腳的反作用力</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>受力相等,小車加速度較大</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>人站地上,重力的反作用力施於？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>槳推水與水推槳</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>平衡力同一物體、作用反作用不同物體</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>地球(人吸引地球)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>划水前進時哪對是作用反作用？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>地面對腳的反作用力</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>槳推水與水推槳</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>大小相等方向相反</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>力對</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>氣墊船或噴射推進共同原理？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>第三</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>推人前進</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>反作用力</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>不同物體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>推進</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>作用反作用力能相加求合力嗎？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>平衡力同一物體、作用反作用不同物體</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>不能,作用在不同物體</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>氣球鬆手飛走與火箭原理相同嗎？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>相同,皆反作用力推進</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>平衡力同一物體、作用反作用不同物體</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>反作用</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>作用反作用力為何不能相加成合力？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>受力相等,小車加速度較大</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>噴氣的反作用力推火箭</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>作用在不同物體</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>作用在不同物體上</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>不同物體</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：B同時也會回推A一個力,這個回推的力就叫反作用力</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>相同：這一對力永遠一樣大,不會一個大一個小</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>反向</t>
+          <t>反向：這一對力方向永遠相反,一個往前一個往後</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>兩物</t>
+          <t>兩物：作用力施加在B身上,反作用力施加在A身上,對象不同</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>不同物體</t>
+          <t>不同物體：因為分別作用在兩個不同的物體上,不會互相抵消</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：腳用力推地面,地面同時也用一樣大的力推回腳,把人推向前</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：火箭把氣體用力往下噴,氣體同時給火箭一個往上的反作用力</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：牛頓第三運動定律,說明的就是這種成對出現的力</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：牛頓第三定律指出,兩物體交互作用時,作用力和反作用力大小相等、方向相反,同時發生</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：子彈受到向前的作用力射出,同時槍也受到大小相等、方向相反的反作用力而後座</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：船槳用力把水往後推,水同時給槳一個往前的反作用力,推動船前進</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>同時</t>
+          <t>同時：這兩個力永遠一起出現、一起消失,不會有先後之分</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>相等</t>
+          <t>相等：不管推多用力,牆壁回推人的力一定跟人推牆的力一樣大</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>關鍵</t>
+          <t>關鍵：作用反作用作用在兩個不同物體上,平衡力則是作用在同一個物體上</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>噴氣</t>
+          <t>噴氣：氣球把空氣往後噴出,空氣同時給氣球一個往前的反作用力使它飛走</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>第三定律</t>
+          <t>第三定律：不管兩車質量差多少,碰撞瞬間彼此互相施加的力大小一定相等</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：手用力把水往後撥,水同時給手一個往前的反作用力,推人前進</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：抵消是指同一物體上的力互相消去,而這兩力分別作用在不同物體上</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：兩手互相拍打時,彼此施加的力互為作用力與反作用力,大小一定相等</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：腳向後蹬地面,地面同時給腳一個大小相等、方向相反的反作用力,推動人向前走</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：火箭前進靠的是噴出氣體時得到的反作用力,不需要空氣幫忙,所以太空中也能飛</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>第二三定律</t>
+          <t>第二三定律：兩車碰撞受力大小一定相等,但小車質量小,同樣的力算出來的加速度比較大</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>區別</t>
+          <t>區別：判斷關鍵在於受力的物體是不是同一個,同一物體上抵消的是平衡力</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：人的腳用力往後蹬地面,地面回推給腳一個向前的反作用力,才讓人往前走</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：地球用重力吸引人,依第三定律,人同樣也用一樣大的力吸引地球</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>力對</t>
+          <t>力對：槳對水施加的推力,和水回推槳的力,這兩個力就是成對的作用反作用力</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>推進</t>
+          <t>推進：不管是氣墊船或噴射引擎,都是靠把氣體往一個方向噴出,得到反方向的推力前進</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：合力只能加總作用在同一個物體上的力,這兩力分別在不同物體上不能相加</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>反作用</t>
+          <t>反作用：氣球和火箭都是把氣體(或燃氣)向後噴出,靠反作用力把自己向前推進,原理相同</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>不同物體</t>
+          <t>不同物體：合力是指作用在「同一個」物體上的多個力才能相加;作用力和反作用力分別作用在兩個不同的物體上,不能相加</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-3_三種難度測驗卷.xlsx
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>相反</t>
+          <t>不同物體</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>作用在不同物體上</t>
+          <t>反作用力</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>不同物體</t>
+          <t>向上</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>相同,皆反作用力推進</t>
+          <t>平衡力同一物體、作用反作用不同物體</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>大小相等方向相反</t>
+          <t>受力相等,小車加速度較大</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>噴氣的反作用力推火箭</t>
+          <t>地面對腳的反作用力</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>作用在不同物體</t>
+          <t>大小相等方向相反</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>平衡力同一物體、作用反作用不同物體</t>
+          <t>受力相等,小車加速度較大</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>受力相等,小車加速度較大</t>
+          <t>相同,皆反作用力推進</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>噴氣的反作用力推火箭</t>
+          <t>槳推水與水推槳</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>作用在不同物體</t>
+          <t>地面對腳的反作用力</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
